--- a/results/milp_solution.xlsx
+++ b/results/milp_solution.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
